--- a/project/excel/excel/LevelGameData.xlsx
+++ b/project/excel/excel/LevelGameData.xlsx
@@ -53,7 +53,7 @@
     <t>当前关卡Boss</t>
   </si>
   <si>
-    <t>哥布林</t>
+    <t>Scarecrow</t>
   </si>
   <si>
     <t>死神</t>
